--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>398</v>
+        <v>185</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G3">
-        <v>411</v>
+        <v>185</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="E2">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>185</v>
+        <v>236</v>
       </c>
       <c r="H3">
         <v>426</v>
